--- a/comparison/eu-health-data-api-ballot-recon-auth/sources/right/CodeSystem-document-priority-category-eu-api.xlsx
+++ b/comparison/eu-health-data-api-ballot-recon-auth/sources/right/CodeSystem-document-priority-category-eu-api.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:01:58+02:00</t>
+    <t>2026-10-23T14:38:45+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
